--- a/artfynd/A 11732-2024 artfynd.xlsx
+++ b/artfynd/A 11732-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127577898</v>
       </c>
       <c r="B2" t="n">
-        <v>102912</v>
+        <v>102913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11732-2024 artfynd.xlsx
+++ b/artfynd/A 11732-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127577898</v>
       </c>
       <c r="B2" t="n">
-        <v>102913</v>
+        <v>102915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11732-2024 artfynd.xlsx
+++ b/artfynd/A 11732-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,6 +790,107 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127818693</v>
+      </c>
+      <c r="B3" t="n">
+        <v>102915</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>836</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dvärgjohannesört</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hypericum humifusum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>900 m SO Fiskarehus, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>402875</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6159595</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Genarp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Staffan Nilsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Staffan Nilsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraövervakning Lund</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 11732-2024 artfynd.xlsx
+++ b/artfynd/A 11732-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127577898</v>
       </c>
       <c r="B2" t="n">
-        <v>102915</v>
+        <v>102921</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>127818693</v>
       </c>
       <c r="B3" t="n">
-        <v>102915</v>
+        <v>102921</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11732-2024 artfynd.xlsx
+++ b/artfynd/A 11732-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127577898</v>
       </c>
       <c r="B2" t="n">
-        <v>102921</v>
+        <v>102924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>127818693</v>
       </c>
       <c r="B3" t="n">
-        <v>102921</v>
+        <v>102924</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11732-2024 artfynd.xlsx
+++ b/artfynd/A 11732-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127577898</v>
       </c>
       <c r="B2" t="n">
-        <v>102924</v>
+        <v>102932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>127818693</v>
       </c>
       <c r="B3" t="n">
-        <v>102924</v>
+        <v>102932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11732-2024 artfynd.xlsx
+++ b/artfynd/A 11732-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127577898</v>
       </c>
       <c r="B2" t="n">
-        <v>102932</v>
+        <v>102933</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>127818693</v>
       </c>
       <c r="B3" t="n">
-        <v>102932</v>
+        <v>102933</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11732-2024 artfynd.xlsx
+++ b/artfynd/A 11732-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127577898</v>
       </c>
       <c r="B2" t="n">
-        <v>102933</v>
+        <v>102934</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>127818693</v>
       </c>
       <c r="B3" t="n">
-        <v>102933</v>
+        <v>102934</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11732-2024 artfynd.xlsx
+++ b/artfynd/A 11732-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127577898</v>
       </c>
       <c r="B2" t="n">
-        <v>102934</v>
+        <v>102935</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>127818693</v>
       </c>
       <c r="B3" t="n">
-        <v>102934</v>
+        <v>102935</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11732-2024 artfynd.xlsx
+++ b/artfynd/A 11732-2024 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127818693</v>
       </c>
       <c r="B3" t="n">
-        <v>102935</v>
+        <v>102943</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11732-2024 artfynd.xlsx
+++ b/artfynd/A 11732-2024 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127818693</v>
       </c>
       <c r="B3" t="n">
-        <v>102943</v>
+        <v>103036</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11732-2024 artfynd.xlsx
+++ b/artfynd/A 11732-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127577898</v>
       </c>
       <c r="B2" t="n">
-        <v>103317</v>
+        <v>103319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11732-2024 artfynd.xlsx
+++ b/artfynd/A 11732-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127577898</v>
       </c>
       <c r="B2" t="n">
-        <v>103319</v>
+        <v>103406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11732-2024 artfynd.xlsx
+++ b/artfynd/A 11732-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127577898</v>
       </c>
       <c r="B2" t="n">
-        <v>103406</v>
+        <v>103409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11732-2024 artfynd.xlsx
+++ b/artfynd/A 11732-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127577898</v>
       </c>
       <c r="B2" t="n">
-        <v>103409</v>
+        <v>103435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11732-2024 artfynd.xlsx
+++ b/artfynd/A 11732-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127577898</v>
       </c>
       <c r="B2" t="n">
-        <v>103435</v>
+        <v>103641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>127818693</v>
       </c>
       <c r="B3" t="n">
-        <v>103036</v>
+        <v>103642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
